--- a/products.xlsx
+++ b/products.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Dulceria-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80D1948-9578-47AA-84B1-0990630C7B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD1AE92-5598-431D-B4E0-78178688BFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="34">
   <si>
     <t>name</t>
   </si>
@@ -118,6 +118,27 @@
   </si>
   <si>
     <t>BABY SHOWER</t>
+  </si>
+  <si>
+    <t>subcategoria</t>
+  </si>
+  <si>
+    <t>Centros de mesa</t>
+  </si>
+  <si>
+    <t>Decoración</t>
+  </si>
+  <si>
+    <t>Piñatas</t>
+  </si>
+  <si>
+    <t>Juguetes</t>
+  </si>
+  <si>
+    <t>Globos</t>
+  </si>
+  <si>
+    <t>Invitaciones</t>
   </si>
 </sst>
 </file>
@@ -435,17 +456,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,16 +481,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -482,16 +507,19 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="F2">
-        <v>85</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G2">
+        <v>85</v>
+      </c>
+      <c r="H2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -505,16 +533,19 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3">
-        <v>85</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="G3">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -528,16 +559,19 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="F4">
-        <v>85</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="G4">
+        <v>85</v>
+      </c>
+      <c r="H4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -551,16 +585,19 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5">
-        <v>85</v>
-      </c>
-      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>85</v>
+      </c>
+      <c r="H5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -574,16 +611,19 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>85</v>
-      </c>
-      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6">
+        <v>85</v>
+      </c>
+      <c r="H6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -597,13 +637,16 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -616,14 +659,14 @@
       <c r="D8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -636,14 +679,14 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -656,14 +699,14 @@
       <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -676,14 +719,14 @@
       <c r="D11" t="s">
         <v>21</v>
       </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -696,14 +739,14 @@
       <c r="D12" t="s">
         <v>21</v>
       </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -716,14 +759,14 @@
       <c r="D13" t="s">
         <v>21</v>
       </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -736,14 +779,14 @@
       <c r="D14" t="s">
         <v>21</v>
       </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -756,14 +799,14 @@
       <c r="D15" t="s">
         <v>21</v>
       </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -776,14 +819,14 @@
       <c r="D16" t="s">
         <v>21</v>
       </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -796,14 +839,14 @@
       <c r="D17" t="s">
         <v>21</v>
       </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -816,14 +859,14 @@
       <c r="D18" t="s">
         <v>21</v>
       </c>
-      <c r="E18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -836,14 +879,14 @@
       <c r="D19" t="s">
         <v>21</v>
       </c>
-      <c r="E19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -856,14 +899,14 @@
       <c r="D20" t="s">
         <v>21</v>
       </c>
-      <c r="E20" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -876,14 +919,14 @@
       <c r="D21" t="s">
         <v>21</v>
       </c>
-      <c r="E21" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -896,14 +939,14 @@
       <c r="D22" t="s">
         <v>21</v>
       </c>
-      <c r="E22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -916,14 +959,14 @@
       <c r="D23" t="s">
         <v>21</v>
       </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -936,14 +979,14 @@
       <c r="D24" t="s">
         <v>21</v>
       </c>
-      <c r="E24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -956,14 +999,14 @@
       <c r="D25" t="s">
         <v>21</v>
       </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -976,14 +1019,14 @@
       <c r="D26" t="s">
         <v>21</v>
       </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -996,14 +1039,14 @@
       <c r="D27" t="s">
         <v>21</v>
       </c>
-      <c r="E27" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1016,14 +1059,14 @@
       <c r="D28" t="s">
         <v>21</v>
       </c>
-      <c r="E28" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1036,14 +1079,14 @@
       <c r="D29" t="s">
         <v>21</v>
       </c>
-      <c r="E29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1056,14 +1099,14 @@
       <c r="D30" t="s">
         <v>21</v>
       </c>
-      <c r="E30" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -1076,14 +1119,14 @@
       <c r="D31" t="s">
         <v>22</v>
       </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1096,14 +1139,14 @@
       <c r="D32" t="s">
         <v>22</v>
       </c>
-      <c r="E32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1116,14 +1159,14 @@
       <c r="D33" t="s">
         <v>22</v>
       </c>
-      <c r="E33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -1136,14 +1179,14 @@
       <c r="D34" t="s">
         <v>22</v>
       </c>
-      <c r="E34" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -1156,14 +1199,14 @@
       <c r="D35" t="s">
         <v>22</v>
       </c>
-      <c r="E35" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -1176,14 +1219,14 @@
       <c r="D36" t="s">
         <v>22</v>
       </c>
-      <c r="E36" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -1196,14 +1239,14 @@
       <c r="D37" t="s">
         <v>22</v>
       </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1216,14 +1259,14 @@
       <c r="D38" t="s">
         <v>22</v>
       </c>
-      <c r="E38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -1236,14 +1279,14 @@
       <c r="D39" t="s">
         <v>22</v>
       </c>
-      <c r="E39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F39">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1256,14 +1299,14 @@
       <c r="D40" t="s">
         <v>22</v>
       </c>
-      <c r="E40" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -1276,14 +1319,14 @@
       <c r="D41" t="s">
         <v>22</v>
       </c>
-      <c r="E41" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -1296,14 +1339,14 @@
       <c r="D42" t="s">
         <v>22</v>
       </c>
-      <c r="E42" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -1316,14 +1359,14 @@
       <c r="D43" t="s">
         <v>22</v>
       </c>
-      <c r="E43" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1336,14 +1379,14 @@
       <c r="D44" t="s">
         <v>22</v>
       </c>
-      <c r="E44" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1356,14 +1399,14 @@
       <c r="D45" t="s">
         <v>22</v>
       </c>
-      <c r="E45" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F45" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -1376,14 +1419,14 @@
       <c r="D46" t="s">
         <v>22</v>
       </c>
-      <c r="E46" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F46" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -1396,14 +1439,14 @@
       <c r="D47" t="s">
         <v>22</v>
       </c>
-      <c r="E47" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F47" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -1416,14 +1459,14 @@
       <c r="D48" t="s">
         <v>22</v>
       </c>
-      <c r="E48" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F48" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -1436,14 +1479,14 @@
       <c r="D49" t="s">
         <v>22</v>
       </c>
-      <c r="E49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F49" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -1456,14 +1499,14 @@
       <c r="D50" t="s">
         <v>22</v>
       </c>
-      <c r="E50" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -1476,14 +1519,14 @@
       <c r="D51" t="s">
         <v>22</v>
       </c>
-      <c r="E51" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -1496,14 +1539,14 @@
       <c r="D52" t="s">
         <v>22</v>
       </c>
-      <c r="E52" t="s">
-        <v>17</v>
-      </c>
-      <c r="F52">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F52" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -1516,14 +1559,14 @@
       <c r="D53" t="s">
         <v>23</v>
       </c>
-      <c r="E53" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -1536,14 +1579,14 @@
       <c r="D54" t="s">
         <v>23</v>
       </c>
-      <c r="E54" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -1556,14 +1599,14 @@
       <c r="D55" t="s">
         <v>23</v>
       </c>
-      <c r="E55" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F55" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>15</v>
       </c>
@@ -1576,14 +1619,14 @@
       <c r="D56" t="s">
         <v>23</v>
       </c>
-      <c r="E56" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F56" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>15</v>
       </c>
@@ -1596,14 +1639,14 @@
       <c r="D57" t="s">
         <v>23</v>
       </c>
-      <c r="E57" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F57" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>15</v>
       </c>
@@ -1616,14 +1659,14 @@
       <c r="D58" t="s">
         <v>23</v>
       </c>
-      <c r="E58" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F58" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -1636,14 +1679,14 @@
       <c r="D59" t="s">
         <v>23</v>
       </c>
-      <c r="E59" t="s">
-        <v>17</v>
-      </c>
-      <c r="F59">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F59" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>15</v>
       </c>
@@ -1656,14 +1699,14 @@
       <c r="D60" t="s">
         <v>23</v>
       </c>
-      <c r="E60" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>15</v>
       </c>
@@ -1676,14 +1719,14 @@
       <c r="D61" t="s">
         <v>23</v>
       </c>
-      <c r="E61" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F61" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -1696,14 +1739,14 @@
       <c r="D62" t="s">
         <v>23</v>
       </c>
-      <c r="E62" t="s">
-        <v>17</v>
-      </c>
-      <c r="F62">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F62" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -1716,14 +1759,14 @@
       <c r="D63" t="s">
         <v>23</v>
       </c>
-      <c r="E63" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F63" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>15</v>
       </c>
@@ -1736,14 +1779,14 @@
       <c r="D64" t="s">
         <v>24</v>
       </c>
-      <c r="E64" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F64" t="s">
+        <v>17</v>
+      </c>
+      <c r="G64">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -1756,14 +1799,14 @@
       <c r="D65" t="s">
         <v>24</v>
       </c>
-      <c r="E65" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>15</v>
       </c>
@@ -1776,14 +1819,14 @@
       <c r="D66" t="s">
         <v>24</v>
       </c>
-      <c r="E66" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F66" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -1796,14 +1839,14 @@
       <c r="D67" t="s">
         <v>24</v>
       </c>
-      <c r="E67" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F67" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -1816,14 +1859,14 @@
       <c r="D68" t="s">
         <v>24</v>
       </c>
-      <c r="E68" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F68" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -1836,14 +1879,14 @@
       <c r="D69" t="s">
         <v>24</v>
       </c>
-      <c r="E69" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F69" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>15</v>
       </c>
@@ -1856,14 +1899,14 @@
       <c r="D70" t="s">
         <v>24</v>
       </c>
-      <c r="E70" t="s">
-        <v>17</v>
-      </c>
-      <c r="F70">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F70" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -1876,14 +1919,14 @@
       <c r="D71" t="s">
         <v>25</v>
       </c>
-      <c r="E71" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F71" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -1896,14 +1939,14 @@
       <c r="D72" t="s">
         <v>25</v>
       </c>
-      <c r="E72" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F72" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -1916,14 +1959,14 @@
       <c r="D73" t="s">
         <v>25</v>
       </c>
-      <c r="E73" t="s">
-        <v>17</v>
-      </c>
-      <c r="F73">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F73" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -1936,14 +1979,14 @@
       <c r="D74" t="s">
         <v>25</v>
       </c>
-      <c r="E74" t="s">
-        <v>17</v>
-      </c>
-      <c r="F74">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F74" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -1956,14 +1999,14 @@
       <c r="D75" t="s">
         <v>26</v>
       </c>
-      <c r="E75" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F75" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -1976,14 +2019,14 @@
       <c r="D76" t="s">
         <v>26</v>
       </c>
-      <c r="E76" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F76" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -1996,14 +2039,14 @@
       <c r="D77" t="s">
         <v>26</v>
       </c>
-      <c r="E77" t="s">
-        <v>17</v>
-      </c>
-      <c r="F77">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F77" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -2016,10 +2059,10 @@
       <c r="D78" t="s">
         <v>26</v>
       </c>
-      <c r="E78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F78">
+      <c r="F78" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78">
         <v>85</v>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B914927C-33B8-4DDE-8EA6-D300019FDD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F23A36-88EE-4562-A9B2-9959466AD41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>name</t>
   </si>
@@ -87,24 +87,6 @@
     <t>Diciembre</t>
   </si>
   <si>
-    <t>BODAS</t>
-  </si>
-  <si>
-    <t>XV AÑOS</t>
-  </si>
-  <si>
-    <t>CUMPLEAÑOS</t>
-  </si>
-  <si>
-    <t>GRADUACIONES</t>
-  </si>
-  <si>
-    <t>BAUTIZOS</t>
-  </si>
-  <si>
-    <t>BABY SHOWER</t>
-  </si>
-  <si>
     <t>subcategoria</t>
   </si>
   <si>
@@ -145,6 +127,15 @@
   </si>
   <si>
     <t>Niños/bluei.jpg</t>
+  </si>
+  <si>
+    <t>Cumpleaños</t>
+  </si>
+  <si>
+    <t>Bautizos</t>
+  </si>
+  <si>
+    <t>Baby Shower</t>
   </si>
 </sst>
 </file>
@@ -488,7 +479,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -500,24 +491,24 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G2">
         <v>85</v>
@@ -528,22 +519,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>85</v>
@@ -563,13 +554,13 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>85</v>
@@ -589,13 +580,13 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
         <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
       </c>
       <c r="G5">
         <v>85</v>
@@ -615,13 +606,13 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>85</v>
@@ -641,13 +632,13 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
         <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
       </c>
       <c r="G7">
         <v>85</v>
@@ -664,7 +655,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -684,7 +675,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -710,32 +701,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F23A36-88EE-4562-A9B2-9959466AD41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428DF91F-1621-4F91-8001-D79375D91797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -711,7 +711,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428DF91F-1621-4F91-8001-D79375D91797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C305F4-0EAE-4FEF-9D94-27B81713C103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
   <si>
     <t>name</t>
   </si>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>Niños/bluei.jpg</t>
-  </si>
-  <si>
-    <t>Cumpleaños</t>
   </si>
   <si>
     <t>Bautizos</t>
@@ -655,7 +652,10 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -676,6 +676,9 @@
       </c>
       <c r="D9" t="s">
         <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -721,12 +724,12 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Nueva carpeta (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C305F4-0EAE-4FEF-9D94-27B81713C103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABFC1E7-E8CD-4449-B471-04E6816F784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
   <si>
     <t>name</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>Baby Shower</t>
+  </si>
+  <si>
+    <t>assets/Niños/Miniboutique.jpeg</t>
   </si>
 </sst>
 </file>
@@ -505,7 +508,7 @@
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G2">
         <v>85</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Nueva carpeta (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABFC1E7-E8CD-4449-B471-04E6816F784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51856950-7271-4E60-BD1E-E3C8E4587E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,12 +114,6 @@
     <t>Graduaciones</t>
   </si>
   <si>
-    <t>Niños/Miniboutique.jpeg</t>
-  </si>
-  <si>
-    <t>Niños/bingo.jpg</t>
-  </si>
-  <si>
     <t>Niños/plimplim.jpg</t>
   </si>
   <si>
@@ -135,7 +129,13 @@
     <t>Baby Shower</t>
   </si>
   <si>
-    <t>assets/Niños/Miniboutique.jpeg</t>
+    <t>src/Niños/Miniboutique.jpeg</t>
+  </si>
+  <si>
+    <t>src/Niños/bingo.jpg</t>
+  </si>
+  <si>
+    <t>src/Piñatas/stich.jpg</t>
   </si>
 </sst>
 </file>
@@ -508,7 +508,7 @@
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2">
         <v>85</v>
@@ -534,7 +534,7 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>85</v>
@@ -560,7 +560,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G4">
         <v>85</v>
@@ -586,7 +586,7 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5">
         <v>85</v>
@@ -612,7 +612,7 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>85</v>
@@ -638,7 +638,7 @@
         <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>85</v>
@@ -684,7 +684,7 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G9">
         <v>85</v>
@@ -727,12 +727,12 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Nueva carpeta (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51856950-7271-4E60-BD1E-E3C8E4587E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF4E4BD-B09C-4F46-BC10-5A0A23A3E0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,9 +75,6 @@
     <t>piñata color azul, 80 cm de altura por 30 de ancho.</t>
   </si>
   <si>
-    <t>Piñatas/stich.jpg</t>
-  </si>
-  <si>
     <t>promo</t>
   </si>
   <si>
@@ -114,28 +111,31 @@
     <t>Graduaciones</t>
   </si>
   <si>
-    <t>Niños/plimplim.jpg</t>
-  </si>
-  <si>
-    <t>Niños/stich.jpg</t>
-  </si>
-  <si>
-    <t>Niños/bluei.jpg</t>
-  </si>
-  <si>
     <t>Bautizos</t>
   </si>
   <si>
     <t>Baby Shower</t>
   </si>
   <si>
-    <t>src/Niños/Miniboutique.jpeg</t>
-  </si>
-  <si>
-    <t>src/Niños/bingo.jpg</t>
-  </si>
-  <si>
     <t>src/Piñatas/stich.jpg</t>
+  </si>
+  <si>
+    <t>./Ninos/Miniboutique.jpeg</t>
+  </si>
+  <si>
+    <t>./Ninos/bingo.jpg</t>
+  </si>
+  <si>
+    <t>./Ninos/plimplim.jpg</t>
+  </si>
+  <si>
+    <t>./Ninos/stich.jpg</t>
+  </si>
+  <si>
+    <t>./Invitaciones/bluei.jpg</t>
+  </si>
+  <si>
+    <t>./Pinatas/stich.jpg</t>
   </si>
 </sst>
 </file>
@@ -479,68 +479,68 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
         <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>75</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G2">
         <v>85</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>75</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G3">
         <v>85</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -554,19 +554,19 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G4">
         <v>85</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -580,19 +580,19 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5">
         <v>85</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -606,19 +606,19 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>85</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -632,13 +632,13 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G7">
         <v>85</v>
@@ -655,13 +655,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>85</v>
@@ -678,13 +678,13 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>85</v>
@@ -707,32 +707,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Nueva carpeta (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF4E4BD-B09C-4F46-BC10-5A0A23A3E0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E59712C-77A7-41DF-B981-F10A70DA2204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,9 +120,6 @@
     <t>src/Piñatas/stich.jpg</t>
   </si>
   <si>
-    <t>./Ninos/Miniboutique.jpeg</t>
-  </si>
-  <si>
     <t>./Ninos/bingo.jpg</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>./Pinatas/stich.jpg</t>
+  </si>
+  <si>
+    <t>src/Ninos/Miniboutique.jpeg</t>
   </si>
 </sst>
 </file>
@@ -459,7 +459,7 @@
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" customWidth="1"/>
     <col min="6" max="6" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -502,13 +502,13 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G2">
         <v>85</v>
@@ -528,13 +528,13 @@
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G3">
         <v>85</v>
@@ -554,13 +554,13 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>85</v>
@@ -580,13 +580,13 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>85</v>
@@ -606,13 +606,13 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6">
         <v>85</v>
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7">
         <v>85</v>
@@ -661,7 +661,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8">
         <v>85</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Nueva carpeta (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E59712C-77A7-41DF-B981-F10A70DA2204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31D2624-A409-4A51-9E8D-5CE1F086B564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,9 +120,6 @@
     <t>src/Piñatas/stich.jpg</t>
   </si>
   <si>
-    <t>./Ninos/bingo.jpg</t>
-  </si>
-  <si>
     <t>./Ninos/plimplim.jpg</t>
   </si>
   <si>
@@ -135,7 +132,10 @@
     <t>./Pinatas/stich.jpg</t>
   </si>
   <si>
-    <t>src/Ninos/Miniboutique.jpeg</t>
+    <t>src/Niños/Miniboutique.jpeg</t>
+  </si>
+  <si>
+    <t>src/Niños/bingo.jpg</t>
   </si>
 </sst>
 </file>
@@ -508,7 +508,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
         <v>85</v>
@@ -534,7 +534,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3">
         <v>85</v>
@@ -560,7 +560,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>85</v>
@@ -586,7 +586,7 @@
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>85</v>
@@ -612,7 +612,7 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>85</v>
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>85</v>
@@ -661,7 +661,7 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>85</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Nueva carpeta (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31D2624-A409-4A51-9E8D-5CE1F086B564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D800624-40E4-4CEE-8B61-71B4A3C82AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
   <si>
     <t>name</t>
   </si>
@@ -54,9 +53,6 @@
     <t>image</t>
   </si>
   <si>
-    <t>CATEGORIAS</t>
-  </si>
-  <si>
     <t>Piñata de Bingo</t>
   </si>
   <si>
@@ -75,13 +71,7 @@
     <t>piñata color azul, 80 cm de altura por 30 de ancho.</t>
   </si>
   <si>
-    <t>promo</t>
-  </si>
-  <si>
-    <t>fecha final de promo</t>
-  </si>
-  <si>
-    <t>Diciembre</t>
+    <t>Piñatas/stich.jpg</t>
   </si>
   <si>
     <t>subcategoria</t>
@@ -102,40 +92,25 @@
     <t>Niños</t>
   </si>
   <si>
-    <t>Bodas</t>
-  </si>
-  <si>
     <t>15 años</t>
   </si>
   <si>
     <t>Graduaciones</t>
   </si>
   <si>
-    <t>Bautizos</t>
-  </si>
-  <si>
-    <t>Baby Shower</t>
-  </si>
-  <si>
-    <t>src/Piñatas/stich.jpg</t>
-  </si>
-  <si>
-    <t>./Ninos/plimplim.jpg</t>
-  </si>
-  <si>
-    <t>./Ninos/stich.jpg</t>
-  </si>
-  <si>
-    <t>./Invitaciones/bluei.jpg</t>
-  </si>
-  <si>
-    <t>./Pinatas/stich.jpg</t>
-  </si>
-  <si>
-    <t>src/Niños/Miniboutique.jpeg</t>
-  </si>
-  <si>
-    <t>src/Niños/bingo.jpg</t>
+    <t>Niños/Miniboutique.jpeg</t>
+  </si>
+  <si>
+    <t>Niños/plimplim.jpg</t>
+  </si>
+  <si>
+    <t>Niños/stich.jpg</t>
+  </si>
+  <si>
+    <t>Niños/bluei.jpg</t>
+  </si>
+  <si>
+    <t>Invitaciones/bingo.jpg</t>
   </si>
 </sst>
 </file>
@@ -453,19 +428,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" customWidth="1"/>
     <col min="6" max="6" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,260 +453,170 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2">
-        <v>85</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3">
-        <v>85</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4">
-        <v>85</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>190</v>
       </c>
       <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5">
-        <v>85</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
       </c>
       <c r="B6">
         <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>85</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>100</v>
       </c>
       <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>100</v>
       </c>
       <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
         <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9">
-        <v>85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0006A038-D07E-48A3-8E00-E138FABFE8CC}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D800624-40E4-4CEE-8B61-71B4A3C82AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069F82F2-BFA4-483B-B7FE-E68C002F27C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>Graduaciones</t>
   </si>
   <si>
-    <t>Niños/Miniboutique.jpeg</t>
-  </si>
-  <si>
     <t>Niños/plimplim.jpg</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>Invitaciones/bingo.jpg</t>
+  </si>
+  <si>
+    <t>Invitaciones/Miniboutique.jpeg</t>
   </si>
 </sst>
 </file>
@@ -476,7 +476,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -496,7 +496,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -516,7 +516,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -536,7 +536,7 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -556,7 +556,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -576,7 +576,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069F82F2-BFA4-483B-B7FE-E68C002F27C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21518115-6EA6-4EF6-99FB-C652E247AD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>name</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Invitaciones/Miniboutique.jpeg</t>
+  </si>
+  <si>
+    <t>Niños/InvitacionMiniboutique1.jpeg</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -476,7 +479,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21518115-6EA6-4EF6-99FB-C652E247AD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A89025E-4959-4C8A-A024-ECB64CC63FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,13 +107,13 @@
     <t>Niños/bluei.jpg</t>
   </si>
   <si>
-    <t>Invitaciones/bingo.jpg</t>
-  </si>
-  <si>
-    <t>Invitaciones/Miniboutique.jpeg</t>
-  </si>
-  <si>
     <t>Niños/InvitacionMiniboutique1.jpeg</t>
+  </si>
+  <si>
+    <t>Niños/InvitacionMiniboutique2.jpeg</t>
+  </si>
+  <si>
+    <t>Niños/InvitacionMiniboutique3.jpeg</t>
   </si>
 </sst>
 </file>
@@ -479,7 +479,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -516,10 +516,10 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A89025E-4959-4C8A-A024-ECB64CC63FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8085DEF7-3902-4A2B-9BC9-6EC5969E546A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
   <si>
     <t>name</t>
   </si>
@@ -107,13 +107,10 @@
     <t>Niños/bluei.jpg</t>
   </si>
   <si>
-    <t>Niños/InvitacionMiniboutique1.jpeg</t>
-  </si>
-  <si>
-    <t>Niños/InvitacionMiniboutique2.jpeg</t>
-  </si>
-  <si>
     <t>Niños/InvitacionMiniboutique3.jpeg</t>
+  </si>
+  <si>
+    <t>Niños/InvitacionMiniboutique1.jpeg, Niños/InvitacionMiniboutique2.jpeg, Niños/InvitacionMiniboutique3.jpeg</t>
   </si>
 </sst>
 </file>
@@ -479,7 +476,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -519,7 +516,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8085DEF7-3902-4A2B-9BC9-6EC5969E546A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073557EC-003D-44DF-A039-CC37D13CA35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>name</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Niños/InvitacionMiniboutique1.jpeg, Niños/InvitacionMiniboutique2.jpeg, Niños/InvitacionMiniboutique3.jpeg</t>
+  </si>
+  <si>
+    <t>Niños/InvitacionMiniboutique1.png, Niños/InvitacionMiniboutique2.png, Niños/InvitacionMiniboutique3.png</t>
   </si>
 </sst>
 </file>
@@ -431,7 +434,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -464,7 +467,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -476,7 +479,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073557EC-003D-44DF-A039-CC37D13CA35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C87906F-F847-4FA3-A205-ECA4E92A637C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>name</t>
   </si>
@@ -56,30 +56,18 @@
     <t>Piñata de Bingo</t>
   </si>
   <si>
-    <t>Piñata de Plim Plim</t>
-  </si>
-  <si>
     <t>piñata color naranja, 80 de alto por 40 de ancho</t>
   </si>
   <si>
-    <t>piñata color roja con blanco, 80 cm de altura por 30 de ancho.</t>
-  </si>
-  <si>
     <t>Piñata de Stich</t>
   </si>
   <si>
     <t>piñata color azul, 80 cm de altura por 30 de ancho.</t>
   </si>
   <si>
-    <t>Piñatas/stich.jpg</t>
-  </si>
-  <si>
     <t>subcategoria</t>
   </si>
   <si>
-    <t>Piñatas</t>
-  </si>
-  <si>
     <t>Invitaciones</t>
   </si>
   <si>
@@ -95,25 +83,23 @@
     <t>15 años</t>
   </si>
   <si>
-    <t>Graduaciones</t>
-  </si>
-  <si>
-    <t>Niños/plimplim.jpg</t>
-  </si>
-  <si>
-    <t>Niños/stich.jpg</t>
-  </si>
-  <si>
     <t>Niños/bluei.jpg</t>
   </si>
   <si>
     <t>Niños/InvitacionMiniboutique3.jpeg</t>
   </si>
   <si>
-    <t>Niños/InvitacionMiniboutique1.jpeg, Niños/InvitacionMiniboutique2.jpeg, Niños/InvitacionMiniboutique3.jpeg</t>
-  </si>
-  <si>
     <t>Niños/InvitacionMiniboutique1.png, Niños/InvitacionMiniboutique2.png, Niños/InvitacionMiniboutique3.png</t>
+  </si>
+  <si>
+    <t>Invitacion Digital 15 Años</t>
+  </si>
+  <si>
+    <t>15 Años</t>
+  </si>
+  <si>
+    <t>15 Años/15 Años
+/Invitacion1.png</t>
   </si>
 </sst>
 </file>
@@ -149,8 +135,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -456,7 +443,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -464,42 +451,42 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -510,116 +497,36 @@
         <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>100</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C87906F-F847-4FA3-A205-ECA4E92A637C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDD6D7F-EA68-46A5-BBBD-680982BDA216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,8 +98,7 @@
     <t>15 Años</t>
   </si>
   <si>
-    <t>15 Años/15 Años
-/Invitacion1.png</t>
+    <t>15 Años/Invitacion1.png</t>
   </si>
 </sst>
 </file>
@@ -135,9 +134,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,7 +483,7 @@
       <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>20</v>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDD6D7F-EA68-46A5-BBBD-680982BDA216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BA4531-7C86-4556-93F5-A44B94CECE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>name</t>
   </si>
@@ -53,18 +53,6 @@
     <t>image</t>
   </si>
   <si>
-    <t>Piñata de Bingo</t>
-  </si>
-  <si>
-    <t>piñata color naranja, 80 de alto por 40 de ancho</t>
-  </si>
-  <si>
-    <t>Piñata de Stich</t>
-  </si>
-  <si>
-    <t>piñata color azul, 80 cm de altura por 30 de ancho.</t>
-  </si>
-  <si>
     <t>subcategoria</t>
   </si>
   <si>
@@ -80,15 +68,6 @@
     <t>Niños</t>
   </si>
   <si>
-    <t>15 años</t>
-  </si>
-  <si>
-    <t>Niños/bluei.jpg</t>
-  </si>
-  <si>
-    <t>Niños/InvitacionMiniboutique3.jpeg</t>
-  </si>
-  <si>
     <t>Niños/InvitacionMiniboutique1.png, Niños/InvitacionMiniboutique2.png, Niños/InvitacionMiniboutique3.png</t>
   </si>
   <si>
@@ -99,6 +78,12 @@
   </si>
   <si>
     <t>15 Años/Invitacion1.png</t>
+  </si>
+  <si>
+    <t>Bodas</t>
+  </si>
+  <si>
+    <t>Bodas/invitacionboda1.avif</t>
   </si>
 </sst>
 </file>
@@ -416,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
@@ -441,7 +426,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -449,81 +434,61 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>130</v>
       </c>
       <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
       <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BA4531-7C86-4556-93F5-A44B94CECE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484B7C8A-7FEB-4890-AE18-112001A96891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>name</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Invitaciones</t>
   </si>
   <si>
-    <t>Invitacion Digital Minni Boutique</t>
-  </si>
-  <si>
     <t>Invitacion Digital Web, incluye conteo regresivo, boton de ubicación, Musica de fondo y confirmacion por Whats app.</t>
   </si>
   <si>
@@ -84,6 +81,12 @@
   </si>
   <si>
     <t>Bodas/invitacionboda1.avif</t>
+  </si>
+  <si>
+    <t>Invitacion Digital Infantil</t>
+  </si>
+  <si>
+    <t>Invitacion Digital Boda</t>
   </si>
 </sst>
 </file>
@@ -434,62 +437,62 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>110</v>
       </c>
       <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\Eventos-y-Celebraciones-GT-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484B7C8A-7FEB-4890-AE18-112001A96891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF10A77-A135-41A4-BD24-720B2C4D6657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>Niños/InvitacionMiniboutique1.png, Niños/InvitacionMiniboutique2.png, Niños/InvitacionMiniboutique3.png</t>
   </si>
   <si>
-    <t>Invitacion Digital 15 Años</t>
-  </si>
-  <si>
     <t>15 Años</t>
   </si>
   <si>
@@ -83,10 +80,13 @@
     <t>Bodas/invitacionboda1.avif</t>
   </si>
   <si>
-    <t>Invitacion Digital Infantil</t>
-  </si>
-  <si>
-    <t>Invitacion Digital Boda</t>
+    <t>Invitación Digital 15 Años</t>
+  </si>
+  <si>
+    <t>Invitación Digital Boda</t>
+  </si>
+  <si>
+    <t>Invitación Digital Niña</t>
   </si>
 </sst>
 </file>
@@ -437,7 +437,7 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>110</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>130</v>
@@ -466,18 +466,18 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>130</v>
@@ -486,13 +486,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
